--- a/Treinamento/15.07 r.xlsx
+++ b/Treinamento/15.07 r.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE03274-R0259540\ICM\Desktop\Subscrição\Robô - Julho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E5BE57-9F3D-4DF8-81D2-0426A239447C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2279C1A-F010-4630-B779-D101C815CA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19330" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,7 +808,7 @@
       <c r="G2" s="6">
         <v>888</v>
       </c>
-      <c r="J2">
+      <c r="H2">
         <v>1032</v>
       </c>
     </row>
@@ -825,7 +825,7 @@
       <c r="G3" s="6">
         <v>1701</v>
       </c>
-      <c r="J3">
+      <c r="H3">
         <v>1036</v>
       </c>
     </row>
@@ -842,7 +842,7 @@
       <c r="G4" s="6">
         <v>1701</v>
       </c>
-      <c r="J4">
+      <c r="H4">
         <v>1027</v>
       </c>
     </row>
@@ -859,7 +859,7 @@
       <c r="G5" s="6">
         <v>1701</v>
       </c>
-      <c r="J5">
+      <c r="H5">
         <v>1030</v>
       </c>
     </row>
@@ -876,7 +876,7 @@
       <c r="G6" s="6">
         <v>1701</v>
       </c>
-      <c r="J6">
+      <c r="H6">
         <v>1021</v>
       </c>
     </row>
@@ -893,7 +893,7 @@
       <c r="G7" s="6">
         <v>1701</v>
       </c>
-      <c r="J7">
+      <c r="H7">
         <v>1015</v>
       </c>
     </row>
@@ -910,7 +910,7 @@
       <c r="G8" s="6">
         <v>1701</v>
       </c>
-      <c r="J8">
+      <c r="H8">
         <v>1012</v>
       </c>
     </row>
@@ -928,7 +928,7 @@
       <c r="G9" s="6">
         <v>1701</v>
       </c>
-      <c r="J9">
+      <c r="H9">
         <v>1015</v>
       </c>
     </row>
@@ -945,7 +945,7 @@
       <c r="G10" s="6">
         <v>1701</v>
       </c>
-      <c r="J10">
+      <c r="H10">
         <v>1012</v>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="G11" s="6">
         <v>1701</v>
       </c>
-      <c r="J11">
+      <c r="H11">
         <v>1036</v>
       </c>
     </row>
@@ -979,7 +979,7 @@
       <c r="G12" s="6">
         <v>1701</v>
       </c>
-      <c r="J12">
+      <c r="H12">
         <v>1021</v>
       </c>
     </row>
@@ -996,7 +996,7 @@
       <c r="G13" s="6">
         <v>1701</v>
       </c>
-      <c r="J13">
+      <c r="H13">
         <v>1033</v>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       <c r="G14" s="6">
         <v>1701</v>
       </c>
-      <c r="J14">
+      <c r="H14">
         <v>1012</v>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       <c r="G15" s="6">
         <v>1701</v>
       </c>
-      <c r="J15">
+      <c r="H15">
         <v>1012</v>
       </c>
     </row>
@@ -1047,11 +1047,11 @@
       <c r="G16" s="6">
         <v>1701</v>
       </c>
-      <c r="J16">
+      <c r="H16">
         <v>1036</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>128301492</v>
       </c>
@@ -1064,11 +1064,11 @@
       <c r="G17" s="6">
         <v>1701</v>
       </c>
-      <c r="J17">
+      <c r="H17">
         <v>1012</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>128340902</v>
       </c>
@@ -1081,11 +1081,11 @@
       <c r="G18" s="6">
         <v>1701</v>
       </c>
-      <c r="J18">
+      <c r="H18">
         <v>1033</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>128309886</v>
       </c>
@@ -1098,11 +1098,11 @@
       <c r="G19" s="6">
         <v>1701</v>
       </c>
-      <c r="J19">
+      <c r="H19">
         <v>1027</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>128314544</v>
       </c>
@@ -1115,11 +1115,11 @@
       <c r="G20" s="6">
         <v>1701</v>
       </c>
-      <c r="J20">
+      <c r="H20">
         <v>1033</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>128314683</v>
       </c>
@@ -1132,11 +1132,11 @@
       <c r="G21" s="6">
         <v>1701</v>
       </c>
-      <c r="J21">
+      <c r="H21">
         <v>1012</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>128317340</v>
       </c>
@@ -1149,11 +1149,11 @@
       <c r="G22" s="6">
         <v>1701</v>
       </c>
-      <c r="J22">
+      <c r="H22">
         <v>1033</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>128317426</v>
       </c>
@@ -1166,11 +1166,11 @@
       <c r="G23" s="6">
         <v>1701</v>
       </c>
-      <c r="J23">
+      <c r="H23">
         <v>1012</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>128320004</v>
       </c>
@@ -1183,11 +1183,11 @@
       <c r="G24" s="6">
         <v>1701</v>
       </c>
-      <c r="J24">
+      <c r="H24">
         <v>1012</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>128320610</v>
       </c>
@@ -1200,11 +1200,11 @@
       <c r="G25" s="6">
         <v>1701</v>
       </c>
-      <c r="J25">
+      <c r="H25">
         <v>1015</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>128002152</v>
       </c>
@@ -1217,11 +1217,11 @@
       <c r="G26" s="6">
         <v>1701</v>
       </c>
-      <c r="J26">
+      <c r="H26">
         <v>1033</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>128327928</v>
       </c>
@@ -1234,11 +1234,11 @@
       <c r="G27" s="6">
         <v>1701</v>
       </c>
-      <c r="J27">
+      <c r="H27">
         <v>1015</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>128328242</v>
       </c>
@@ -1251,11 +1251,11 @@
       <c r="G28" s="6">
         <v>1701</v>
       </c>
-      <c r="J28">
+      <c r="H28">
         <v>1015</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>128329625</v>
       </c>
@@ -1268,11 +1268,11 @@
       <c r="G29" s="6">
         <v>1701</v>
       </c>
-      <c r="J29">
+      <c r="H29">
         <v>1018</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>128329698</v>
       </c>
@@ -1285,11 +1285,11 @@
       <c r="G30" s="6">
         <v>1701</v>
       </c>
-      <c r="J30">
+      <c r="H30">
         <v>1018</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>128330570</v>
       </c>
@@ -1302,11 +1302,11 @@
       <c r="G31" s="6">
         <v>1701</v>
       </c>
-      <c r="J31">
+      <c r="H31">
         <v>1027</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>128330922</v>
       </c>
@@ -1319,11 +1319,11 @@
       <c r="G32" s="6">
         <v>1701</v>
       </c>
-      <c r="J32">
+      <c r="H32">
         <v>1015</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>128331006</v>
       </c>
@@ -1336,11 +1336,11 @@
       <c r="G33" s="6">
         <v>1701</v>
       </c>
-      <c r="J33">
+      <c r="H33">
         <v>1030</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>128331169</v>
       </c>
@@ -1353,11 +1353,11 @@
       <c r="G34" s="6">
         <v>1701</v>
       </c>
-      <c r="J34">
+      <c r="H34">
         <v>1027</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>128384106</v>
       </c>
@@ -1370,11 +1370,11 @@
       <c r="G35" s="6">
         <v>2279</v>
       </c>
-      <c r="J35">
+      <c r="H35">
         <v>1021</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>128217514</v>
       </c>
@@ -1387,11 +1387,11 @@
       <c r="G36" s="6">
         <v>8002</v>
       </c>
-      <c r="J36">
+      <c r="H36">
         <v>1036</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>128264778</v>
       </c>
@@ -1404,11 +1404,11 @@
       <c r="G37" s="6">
         <v>8002</v>
       </c>
-      <c r="J37">
+      <c r="H37">
         <v>1015</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>128299452</v>
       </c>
@@ -1421,11 +1421,11 @@
       <c r="G38" s="6">
         <v>714</v>
       </c>
-      <c r="J38">
+      <c r="H38">
         <v>995</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>128280385</v>
       </c>
@@ -1438,11 +1438,11 @@
       <c r="G39" s="6">
         <v>1701</v>
       </c>
-      <c r="J39">
+      <c r="H39">
         <v>994</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>128281155</v>
       </c>
@@ -1455,11 +1455,11 @@
       <c r="G40" s="6">
         <v>1701</v>
       </c>
-      <c r="J40">
+      <c r="H40">
         <v>996</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>128283683</v>
       </c>
@@ -1472,11 +1472,11 @@
       <c r="G41" s="6">
         <v>1701</v>
       </c>
-      <c r="J41">
+      <c r="H41">
         <v>998</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>128310470</v>
       </c>
@@ -1489,11 +1489,11 @@
       <c r="G42" s="6">
         <v>1701</v>
       </c>
-      <c r="J42">
+      <c r="H42">
         <v>1006</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>128262052</v>
       </c>
@@ -1506,11 +1506,11 @@
       <c r="G43" s="6">
         <v>1701</v>
       </c>
-      <c r="J43">
+      <c r="H43">
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>128262377</v>
       </c>
@@ -1523,11 +1523,11 @@
       <c r="G44" s="6">
         <v>1701</v>
       </c>
-      <c r="J44">
+      <c r="H44">
         <v>1010</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>128263957</v>
       </c>
@@ -1540,11 +1540,11 @@
       <c r="G45" s="6">
         <v>1701</v>
       </c>
-      <c r="J45">
+      <c r="H45">
         <v>996</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>128278725</v>
       </c>
@@ -1557,11 +1557,11 @@
       <c r="G46" s="6">
         <v>1701</v>
       </c>
-      <c r="J46">
+      <c r="H46">
         <v>994</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>128282812</v>
       </c>
@@ -1574,11 +1574,11 @@
       <c r="G47" s="6">
         <v>1701</v>
       </c>
-      <c r="J47">
+      <c r="H47">
         <v>1008</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>128292067</v>
       </c>
@@ -1591,11 +1591,11 @@
       <c r="G48" s="6">
         <v>1701</v>
       </c>
-      <c r="J48">
+      <c r="H48">
         <v>1000</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>128292077</v>
       </c>
@@ -1608,11 +1608,11 @@
       <c r="G49" s="6">
         <v>1701</v>
       </c>
-      <c r="J49">
+      <c r="H49">
         <v>1006</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>128293234</v>
       </c>
@@ -1625,11 +1625,11 @@
       <c r="G50" s="6">
         <v>1701</v>
       </c>
-      <c r="J50">
+      <c r="H50">
         <v>996</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>128294520</v>
       </c>
@@ -1642,11 +1642,11 @@
       <c r="G51" s="6">
         <v>1701</v>
       </c>
-      <c r="J51">
+      <c r="H51">
         <v>998</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>128296437</v>
       </c>
@@ -1659,11 +1659,11 @@
       <c r="G52" s="6">
         <v>1701</v>
       </c>
-      <c r="J52">
+      <c r="H52">
         <v>1004</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>128296570</v>
       </c>
@@ -1676,11 +1676,11 @@
       <c r="G53" s="6">
         <v>1701</v>
       </c>
-      <c r="J53">
+      <c r="H53">
         <v>998</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>128300417</v>
       </c>
@@ -1693,11 +1693,11 @@
       <c r="G54" s="6">
         <v>1701</v>
       </c>
-      <c r="J54">
+      <c r="H54">
         <v>1010</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>128301027</v>
       </c>
@@ -1710,11 +1710,11 @@
       <c r="G55" s="6">
         <v>1701</v>
       </c>
-      <c r="J55">
+      <c r="H55">
         <v>1010</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>128306852</v>
       </c>
@@ -1727,11 +1727,11 @@
       <c r="G56" s="6">
         <v>1701</v>
       </c>
-      <c r="J56">
+      <c r="H56">
         <v>998</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>128311876</v>
       </c>
@@ -1744,11 +1744,11 @@
       <c r="G57" s="6">
         <v>1701</v>
       </c>
-      <c r="J57">
+      <c r="H57">
         <v>994</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>128321532</v>
       </c>
@@ -1761,11 +1761,11 @@
       <c r="G58" s="6">
         <v>1701</v>
       </c>
-      <c r="J58">
+      <c r="H58">
         <v>1010</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>128327073</v>
       </c>
@@ -1778,11 +1778,11 @@
       <c r="G59" s="6">
         <v>1701</v>
       </c>
-      <c r="J59">
+      <c r="H59">
         <v>1006</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>128328474</v>
       </c>
@@ -1795,11 +1795,11 @@
       <c r="G60" s="6">
         <v>1701</v>
       </c>
-      <c r="J60">
+      <c r="H60">
         <v>996</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>125574319</v>
       </c>
@@ -1812,11 +1812,11 @@
       <c r="G61" s="6">
         <v>2279</v>
       </c>
-      <c r="J61">
+      <c r="H61">
         <v>994</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>126853062</v>
       </c>
@@ -1829,11 +1829,11 @@
       <c r="G62" s="6">
         <v>2279</v>
       </c>
-      <c r="J62">
+      <c r="H62">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>128383697</v>
       </c>
@@ -1846,11 +1846,11 @@
       <c r="G63" s="6">
         <v>2279</v>
       </c>
-      <c r="J63">
+      <c r="H63">
         <v>996</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>128389981</v>
       </c>
@@ -1863,7 +1863,7 @@
       <c r="G64" s="6">
         <v>2279</v>
       </c>
-      <c r="J64">
+      <c r="H64">
         <v>998</v>
       </c>
     </row>
@@ -1919,31 +1919,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8378E04A-2A0A-4D9C-AD0A-883FECC74A4C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>